--- a/scripts/test-data/test-data-004-mockpass-import-demo.xlsx
+++ b/scripts/test-data/test-data-004-mockpass-import-demo.xlsx
@@ -460,12 +460,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.996339" customWidth="1" style="4" min="1" max="1"/>
     <col width="14.282054" customWidth="1" style="4" min="2" max="2"/>
-    <col width="15.282054" customWidth="1" style="4" min="3" max="3"/>
+    <col width="42" customWidth="1" style="4" min="3" max="3"/>
     <col width="28.139196" customWidth="1" style="4" min="4" max="4"/>
     <col width="11.424911" customWidth="1" style="5" min="5" max="5"/>
     <col width="15.282054" customWidth="1" style="4" min="6" max="6"/>
@@ -494,70 +494,75 @@
       </c>
       <c r="C1" s="6" t="inlineStr">
         <is>
+          <t>MockPassPersonId</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
           <t>IdentityNumber</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>FullName</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>DateOfBirth</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>NationalityCode</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>CitizenshipStatusCode</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>StudentNumber</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>AcademicYear</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>LevelCode</t>
         </is>
       </c>
-      <c r="K1" s="6" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>ClassCode</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>StartDate</t>
         </is>
       </c>
-      <c r="M1" s="6" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="N1" s="6" t="inlineStr">
+      <c r="O1" s="6" t="inlineStr">
         <is>
           <t>Mobile</t>
         </is>
       </c>
-      <c r="O1" s="6" t="inlineStr">
+      <c r="P1" s="6" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="P1" s="6" t="inlineStr">
+      <c r="Q1" s="6" t="inlineStr">
         <is>
           <t>TemplateRow</t>
         </is>
@@ -570,61 +575,66 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
+          <t>3c47624e-f746-5c1e-a09a-93610f1c050c</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
           <t>S7000081M</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO004 Elias Goh NUS</t>
         </is>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="F2" s="5" t="n">
         <v>39339</v>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>NUS-2026-081</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>NUS-S3-17</t>
         </is>
       </c>
-      <c r="L2" s="5" t="n">
+      <c r="M2" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo004.elias.goh.nus.081@student.example.test</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>+6591000081</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>81 Education Avenue, Singapore 100081</t>
         </is>
@@ -637,61 +647,66 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
+          <t>205a6627-daac-5ae7-99b1-f8058861c713</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
           <t>S7000082N</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO004 Farah Rahman NTU</t>
         </is>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="F3" s="5" t="n">
         <v>37287</v>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>NTU-2026-082</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>NTU-P6-17</t>
         </is>
       </c>
-      <c r="L3" s="5" t="n">
+      <c r="M3" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo004.farah.rahman.ntu.082@student.example.test</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>+6591000082</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>82 Education Avenue, Singapore 100082</t>
         </is>
@@ -704,61 +719,66 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
+          <t>6805378b-e41d-51cf-864c-99f22a785ec0</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
           <t>S7000083P</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO004 Gideon Koh SMU</t>
         </is>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="F4" s="5" t="n">
         <v>40152</v>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>SMU-2026-083</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>SMU-S2-17</t>
         </is>
       </c>
-      <c r="L4" s="5" t="n">
+      <c r="M4" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo004.gideon.koh.smu.083@student.example.test</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>+6591000083</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>83 Education Avenue, Singapore 100083</t>
         </is>
@@ -771,61 +791,66 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
+          <t>04bbd5eb-b758-52b0-8294-2e712becc713</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
           <t>S7000084Q</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO004 Hazel Ng SUTD</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="F5" s="5" t="n">
         <v>37094</v>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>SUTD-2026-084</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>BACHELOR</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>SUTD-UG-17</t>
         </is>
       </c>
-      <c r="L5" s="5" t="n">
+      <c r="M5" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo004.hazel.ng.sutd.084@student.example.test</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>+6591000084</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>84 Education Avenue, Singapore 100084</t>
         </is>
@@ -838,61 +863,66 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
+          <t>d9e16caa-e021-5084-8e89-0dbf12306340</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
           <t>S7000085R</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO004 Isaac Chua SIT</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="F6" s="5" t="n">
         <v>35506</v>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>SIT-2026-085</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>MASTER</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>SIT-PG-17</t>
         </is>
       </c>
-      <c r="L6" s="5" t="n">
+      <c r="M6" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo004.isaac.chua.sit.085@student.example.test</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>+6591000085</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>85 Education Avenue, Singapore 100085</t>
         </is>
@@ -905,61 +935,66 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
+          <t>c6ce32bc-81d4-5487-8ed1-f892f9a78575</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
           <t>S7000086T</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO004 Jia Min Seah NUS</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="F7" s="5" t="n">
         <v>39730</v>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>NUS-2026-086</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>PHD</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>NUS-DR-18</t>
         </is>
       </c>
-      <c r="L7" s="5" t="n">
+      <c r="M7" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo004.jia.min.seah.nus.086@student.example.test</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>+6591000086</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="P7" s="4" t="inlineStr">
         <is>
           <t>86 Education Avenue, Singapore 100086</t>
         </is>
@@ -972,61 +1007,66 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
+          <t>e8490043-621c-5656-9de6-c4eeeb778750</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
           <t>S7000087U</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO004 Keira Low NTU</t>
         </is>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="F8" s="5" t="n">
         <v>37729</v>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>NTU-2026-087</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>BACHELOR</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>NTU-UG-18</t>
         </is>
       </c>
-      <c r="L8" s="5" t="n">
+      <c r="M8" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo004.keira.low.ntu.087@student.example.test</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>+6591000087</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="P8" s="4" t="inlineStr">
         <is>
           <t>87 Education Avenue, Singapore 100087</t>
         </is>
@@ -1039,61 +1079,66 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
+          <t>c499db6e-053d-5ed6-9906-9e54643572fe</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
           <t>S7000088V</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO004 Leon Ho SMU</t>
         </is>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="F9" s="5" t="n">
         <v>36336</v>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>SMU-2026-088</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>MASTER</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>SMU-PG-18</t>
         </is>
       </c>
-      <c r="L9" s="5" t="n">
+      <c r="M9" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo004.leon.ho.smu.088@student.example.test</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>+6591000088</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="P9" s="4" t="inlineStr">
         <is>
           <t>88 Education Avenue, Singapore 100088</t>
         </is>
@@ -1106,61 +1151,66 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
+          <t>b160d9ac-cbd3-5ee0-b2fd-0d3125feec5b</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
           <t>S7000089W</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO004 Mira Das SUTD</t>
         </is>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="F10" s="5" t="n">
         <v>34676</v>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>SUTD-2026-089</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>PHD</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>SUTD-DR-18</t>
         </is>
       </c>
-      <c r="L10" s="5" t="n">
+      <c r="M10" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo004.mira.das.sutd.089@student.example.test</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>+6591000089</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="P10" s="4" t="inlineStr">
         <is>
           <t>89 Education Avenue, Singapore 100089</t>
         </is>
@@ -1173,61 +1223,66 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
+          <t>5476dac7-48ef-5175-ac9d-aba2c57a8130</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
           <t>S7000090X</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO004 Nolan Teo SIT</t>
         </is>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="F11" s="5" t="n">
         <v>38797</v>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>SIT-2026-090</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>SIT-S4-18</t>
         </is>
       </c>
-      <c r="L11" s="5" t="n">
+      <c r="M11" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo004.nolan.teo.sit.090@student.example.test</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="O11" s="4" t="inlineStr">
         <is>
           <t>+6591000090</t>
         </is>
       </c>
-      <c r="O11" s="4" t="inlineStr">
+      <c r="P11" s="4" t="inlineStr">
         <is>
           <t>90 Education Avenue, Singapore 100090</t>
         </is>
@@ -1240,61 +1295,66 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
+          <t>6361e233-6cc7-5e21-995e-b3beeb1ccca6</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
           <t>S7000091Y</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO004 Olivia Chan NUS</t>
         </is>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="F12" s="5" t="n">
         <v>40309</v>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>NUS-2026-091</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>NUS-S3-19</t>
         </is>
       </c>
-      <c r="L12" s="5" t="n">
+      <c r="M12" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="N12" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo004.olivia.chan.nus.091@student.example.test</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>+6591000091</t>
         </is>
       </c>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="P12" s="4" t="inlineStr">
         <is>
           <t>91 Education Avenue, Singapore 100091</t>
         </is>
@@ -1307,61 +1367,66 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
+          <t>3628ac43-794f-536d-8a50-2a41cf6a477f</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
           <t>S7000092Z</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO004 Pranav Menon NTU</t>
         </is>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="F13" s="5" t="n">
         <v>36799</v>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>NTU-2026-092</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>NTU-P6-19</t>
         </is>
       </c>
-      <c r="L13" s="5" t="n">
+      <c r="M13" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo004.pranav.menon.ntu.092@student.example.test</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="O13" s="4" t="inlineStr">
         <is>
           <t>+6591000092</t>
         </is>
       </c>
-      <c r="O13" s="4" t="inlineStr">
+      <c r="P13" s="4" t="inlineStr">
         <is>
           <t>92 Education Avenue, Singapore 100092</t>
         </is>
@@ -1374,61 +1439,66 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
+          <t>0c72de46-9a00-5a07-8072-f1462f6a1da0</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
           <t>S7000093A</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO004 Renee Yap SMU</t>
         </is>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="F14" s="5" t="n">
         <v>35080</v>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>SMU-2026-093</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>SMU-S2-19</t>
         </is>
       </c>
-      <c r="L14" s="5" t="n">
+      <c r="M14" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo004.renee.yap.smu.093@student.example.test</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>+6591000093</t>
         </is>
       </c>
-      <c r="O14" s="4" t="inlineStr">
+      <c r="P14" s="4" t="inlineStr">
         <is>
           <t>93 Education Avenue, Singapore 100093</t>
         </is>
@@ -1441,61 +1511,66 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
+          <t>14e99df3-3e63-5b84-96fd-8a9e548fd38c</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
           <t>S7000094B</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO004 Samuel Tay SUTD</t>
         </is>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="F15" s="5" t="n">
         <v>38175</v>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>SUTD-2026-094</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>BACHELOR</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>SUTD-UG-19</t>
         </is>
       </c>
-      <c r="L15" s="5" t="n">
+      <c r="M15" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="N15" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo004.samuel.tay.sutd.094@student.example.test</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="O15" s="4" t="inlineStr">
         <is>
           <t>+6591000094</t>
         </is>
       </c>
-      <c r="O15" s="4" t="inlineStr">
+      <c r="P15" s="4" t="inlineStr">
         <is>
           <t>94 Education Avenue, Singapore 100094</t>
         </is>
@@ -1508,61 +1583,66 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
+          <t>5025d6a3-7402-5495-8553-a6890bc21070</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
           <t>S7000095C</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO004 Tara Nair SIT</t>
         </is>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="F16" s="5" t="n">
         <v>39775</v>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>SIT-2026-095</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>MASTER</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>SIT-PG-19</t>
         </is>
       </c>
-      <c r="L16" s="5" t="n">
+      <c r="M16" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo004.tara.nair.sit.095@student.example.test</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>+6591000095</t>
         </is>
       </c>
-      <c r="O16" s="4" t="inlineStr">
+      <c r="P16" s="4" t="inlineStr">
         <is>
           <t>95 Education Avenue, Singapore 100095</t>
         </is>
@@ -1575,61 +1655,66 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
+          <t>d396c0da-bd95-59e2-b47f-6bfb1598ae1e</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
           <t>S7000096D</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO004 Vikram Singh NUS</t>
         </is>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="F17" s="5" t="n">
         <v>37531</v>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>NUS-2026-096</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>PHD</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>NUS-DR-20</t>
         </is>
       </c>
-      <c r="L17" s="5" t="n">
+      <c r="M17" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo004.vikram.singh.nus.096@student.example.test</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>+6591000096</t>
         </is>
       </c>
-      <c r="O17" s="4" t="inlineStr">
+      <c r="P17" s="4" t="inlineStr">
         <is>
           <t>96 Education Avenue, Singapore 100096</t>
         </is>
@@ -1642,61 +1727,66 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
+          <t>1b67f04d-1716-5fc5-87f9-28e5470795ce</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
           <t>S7000097E</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO004 Avery Tan NTU</t>
         </is>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="F18" s="5" t="n">
         <v>38029</v>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>NTU-2026-097</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>BACHELOR</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>NTU-UG-20</t>
         </is>
       </c>
-      <c r="L18" s="5" t="n">
+      <c r="M18" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo004.avery.tan.ntu.097@student.example.test</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>+6591000097</t>
         </is>
       </c>
-      <c r="O18" s="4" t="inlineStr">
+      <c r="P18" s="4" t="inlineStr">
         <is>
           <t>97 Education Avenue, Singapore 100097</t>
         </is>
@@ -1707,63 +1797,64 @@
       <c r="B19" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>A7000098F</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO004 Bianca Lim SMU</t>
         </is>
       </c>
-      <c r="E19" s="5" t="n">
+      <c r="F19" s="5" t="n">
         <v>36010</v>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>SMU-2026-098</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>MASTER</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>SMU-PG-20</t>
         </is>
       </c>
-      <c r="L19" s="5" t="n">
+      <c r="M19" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo004.bianca.lim.smu.098@student.example.test</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="O19" s="4" t="inlineStr">
         <is>
           <t>+6591000098</t>
         </is>
       </c>
-      <c r="O19" s="4" t="inlineStr">
+      <c r="P19" s="4" t="inlineStr">
         <is>
           <t>98 Education Avenue, Singapore 100098</t>
         </is>
@@ -1776,57 +1867,62 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
+          <t>4ef563fd-d4bc-5c32-b2a4-d20a0be0a56f</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
           <t>S7000099G</t>
         </is>
       </c>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="5" t="n">
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="5" t="n">
         <v>34292</v>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>SUTD-2026-099</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>PHD</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>SUTD-DR-20</t>
         </is>
       </c>
-      <c r="L20" s="5" t="n">
+      <c r="M20" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo004.caleb.wong.sutd.099@student.example.test</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>+6591000099</t>
         </is>
       </c>
-      <c r="O20" s="4" t="inlineStr">
+      <c r="P20" s="4" t="inlineStr">
         <is>
           <t>99 Education Avenue, Singapore 100099</t>
         </is>
@@ -1839,61 +1935,66 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
+          <t>74b2b1fc-6915-590e-9f0a-a9d3d92525d1</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
           <t>S7000100H</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO004 Daphne Lee SIT</t>
         </is>
       </c>
-      <c r="E21" s="5" t="n">
+      <c r="F21" s="5" t="n">
         <v>38500</v>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>SIT-2026-100</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>SIT-S4-20</t>
         </is>
       </c>
-      <c r="L21" s="5" t="n">
+      <c r="M21" s="5" t="n">
         <v>38135</v>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo004.daphne.lee.sit.100@student.example.test</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="O21" s="4" t="inlineStr">
         <is>
           <t>+6591000100</t>
         </is>
       </c>
-      <c r="O21" s="4" t="inlineStr">
+      <c r="P21" s="4" t="inlineStr">
         <is>
           <t>100 Education Avenue, Singapore 100100</t>
         </is>
